--- a/public/DCF_Valuation.xlsx
+++ b/public/DCF_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varun\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\varun\Documents\student-portfolio\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8184771-75D1-45D0-A11B-198709F308AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EFF4BCA9-B4AF-4A4F-A2B2-E60E9F633F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{16287448-6C2A-45C9-A604-AE5C715270A4}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="106">
   <si>
     <t>Assumptions</t>
   </si>
@@ -124,9 +124,6 @@
     <t>Operating Current Assets = Marketable Securities(18,763)+Accounts Receivable(39,777)+Vendor Receivables(33,180)+Inventory(5,718)+Other Current Assets(14,585) =$ 112,023</t>
   </si>
   <si>
-    <t>NWC Calculation(2025)</t>
-  </si>
-  <si>
     <t>Operating Current Liabilities = 69,860(Accounts Payable)+Other Current Liabilities(66,387)+Deffered Revenue(9,055) = $145,302</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>NWC Calculation(2024)</t>
-  </si>
-  <si>
     <t>Operating Current Assets = 35,228+33,410+32,833+7,286+14,287=123,044</t>
   </si>
   <si>
@@ -323,6 +317,62 @@
   </si>
   <si>
     <t>Apple Inc.(AAPL) historical and current market price information</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Historical Average</t>
+  </si>
+  <si>
+    <t>Effective Tax Rate</t>
+  </si>
+  <si>
+    <t>CAPM estimate</t>
+  </si>
+  <si>
+    <t>FY2025 10-K</t>
+  </si>
+  <si>
+    <t>Long-term GDP</t>
+  </si>
+  <si>
+    <t>2025 actual</t>
+  </si>
+  <si>
+    <t>Calc</t>
+  </si>
+  <si>
+    <r>
+      <t>●NWC Calculation(2025)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>●</t>
+    </r>
+  </si>
+  <si>
+    <t>●NWC Calculation(2024)●</t>
+  </si>
+  <si>
+    <t>2024 NWC=-32469</t>
+  </si>
+  <si>
+    <t>Set to -8.10%</t>
+  </si>
+  <si>
+    <t>Operating NWC(%Revenue) Numbers</t>
+  </si>
+  <si>
+    <t>Click to expand——————&gt;</t>
+  </si>
+  <si>
+    <t>Click to expand------&gt;</t>
   </si>
 </sst>
 </file>
@@ -334,9 +384,9 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -407,16 +457,71 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -531,39 +636,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -573,80 +697,130 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -986,291 +1160,339 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="E3:W34"/>
+  <dimension ref="E3:V34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="5:13" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6" t="s">
+    <row r="3" spans="5:14" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="5:13" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5" t="s">
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+    </row>
+    <row r="4" spans="5:14" ht="25.8" x14ac:dyDescent="0.5">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="5:13" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="8" t="s">
+      <c r="N4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="5:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="10">
+      <c r="H5" s="5"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="7">
         <v>4.2000000000000003E-2</v>
       </c>
-    </row>
-    <row r="6" spans="5:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="11" t="s">
+      <c r="N5" s="35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="5:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="12">
+      <c r="H6" s="8"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="9">
         <v>0.311</v>
       </c>
-    </row>
-    <row r="7" spans="5:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="13" t="s">
+      <c r="N6" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="5:14" ht="21" x14ac:dyDescent="0.4">
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="12">
+      <c r="H7" s="10"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="9">
         <v>0.18099999999999999</v>
       </c>
-    </row>
-    <row r="8" spans="5:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="E8" s="14" t="s">
+      <c r="N7" s="36" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="5:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="E8" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="12">
+      <c r="F8" s="70"/>
+      <c r="G8" s="70"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="70"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="9">
         <v>2.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="9" spans="5:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="E9" s="5"/>
-      <c r="F9" s="14" t="s">
+      <c r="N8" s="36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="5:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="E9" s="3"/>
+      <c r="F9" s="70" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="12">
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="70"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="9">
         <v>2.9000000000000001E-2</v>
       </c>
-    </row>
-    <row r="10" spans="5:13" ht="21" x14ac:dyDescent="0.4">
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="13" t="s">
+      <c r="N9" s="36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="5:14" ht="21" x14ac:dyDescent="0.4">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="12">
+      <c r="H10" s="10"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="9">
         <v>8.5000000000000006E-2</v>
       </c>
-    </row>
-    <row r="11" spans="5:13" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="15" t="s">
+      <c r="N10" s="36" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="5:14" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="17">
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="9">
         <v>2.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="12" spans="5:13" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="G12" s="28"/>
-      <c r="H12" s="29" t="s">
+      <c r="N11" s="36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="5:14" ht="23.4" x14ac:dyDescent="0.45">
+      <c r="H12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-      <c r="M12" s="30">
+      <c r="M12" s="21">
         <v>14900</v>
       </c>
-    </row>
-    <row r="13" spans="5:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="G13" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="32">
+      <c r="N12" s="36" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="5:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="G13" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="23">
         <v>-8.1000000000000003E-2</v>
       </c>
-    </row>
-    <row r="19" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="N13" s="37" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="7:22" x14ac:dyDescent="0.3">
       <c r="G19" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G20" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="67"/>
+      <c r="I20" s="67"/>
+    </row>
+    <row r="21" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G21" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="38"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="38"/>
+      <c r="K21" s="38"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="38"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="38"/>
+      <c r="S21" s="38"/>
+      <c r="T21" s="38"/>
+      <c r="U21" s="38"/>
+      <c r="V21" s="38"/>
+    </row>
+    <row r="22" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G22" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="68"/>
+      <c r="I22" s="68"/>
+      <c r="J22" s="68"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
+      <c r="M22" s="68"/>
+      <c r="N22" s="68"/>
+      <c r="O22" s="68"/>
+      <c r="P22" s="68"/>
+      <c r="Q22" s="68"/>
+      <c r="R22" s="68"/>
+      <c r="S22" s="38"/>
+      <c r="T22" s="38"/>
+      <c r="U22" s="38"/>
+      <c r="V22" s="38"/>
+    </row>
+    <row r="23" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G23" s="40" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="40"/>
+    </row>
+    <row r="24" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G25" s="38" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="20" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G24" t="s">
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="38"/>
+      <c r="M25" s="38"/>
+    </row>
+    <row r="26" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G26" s="38" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="25" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G25" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="27" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G27">
-        <f>123044-155513</f>
-        <v>-32469</v>
-      </c>
-    </row>
-    <row r="29" spans="7:23" x14ac:dyDescent="0.3">
+      <c r="H26" s="38"/>
+      <c r="I26" s="38"/>
+      <c r="J26" s="38"/>
+      <c r="K26" s="38"/>
+      <c r="L26" s="38"/>
+      <c r="M26" s="38"/>
+    </row>
+    <row r="27" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G27" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="H27" s="66"/>
+    </row>
+    <row r="28" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G28" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+    </row>
+    <row r="29" spans="7:22" x14ac:dyDescent="0.3">
       <c r="G29">
         <v>2024</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G30" s="27">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G30" s="20">
         <f>-32469/391035</f>
         <v>-8.3033488050941726E-2</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="2">
         <v>-8.1500000000000003E-2</v>
       </c>
     </row>
-    <row r="31" spans="7:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="7:22" x14ac:dyDescent="0.3">
       <c r="G31">
         <v>2025</v>
       </c>
-    </row>
-    <row r="32" spans="7:23" x14ac:dyDescent="0.3">
-      <c r="G32" s="27">
+      <c r="I31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="7:22" x14ac:dyDescent="0.3">
+      <c r="G32" s="20">
         <f>33279/416161</f>
         <v>7.9966647523434436E-2</v>
       </c>
     </row>
     <row r="34" spans="7:10" x14ac:dyDescent="0.3">
-      <c r="G34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
+      <c r="G34" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="69"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G22:R22"/>
+  <mergeCells count="8">
     <mergeCell ref="G34:J34"/>
     <mergeCell ref="F9:J9"/>
     <mergeCell ref="E8:J8"/>
     <mergeCell ref="H3:J3"/>
     <mergeCell ref="H4:J4"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G22:R22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="46" orientation="portrait" r:id="rId1"/>
@@ -1290,322 +1512,322 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
+      <c r="A2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="17">
         <v>416161</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="17">
         <f>B3*(1+Assumptions!$M$5)</f>
         <v>433639.76199999999</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="17">
         <f>C3*(1+Assumptions!$M$5)</f>
         <v>451852.63200400001</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="17">
         <f>D3*(1+Assumptions!$M$5)</f>
         <v>470830.44254816801</v>
       </c>
-      <c r="F3" s="24">
+      <c r="F3" s="17">
         <f>E3*(1+Assumptions!$M$5)</f>
         <v>490605.32113519107</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="17">
         <f>F3*(1+Assumptions!$M$5)</f>
         <v>511210.74462286913</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="20"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="17">
         <v>133050</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="17">
         <f>C3*Assumptions!$M$6</f>
         <v>134861.96598199999</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="17">
         <f>D3*Assumptions!$M$6</f>
         <v>140526.168553244</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="17">
         <f>E3*Assumptions!$M$6</f>
         <v>146428.26763248025</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="17">
         <f>F3*Assumptions!$M$6</f>
         <v>152578.25487304441</v>
       </c>
-      <c r="G5" s="24">
+      <c r="G5" s="17">
         <f>G3*Assumptions!$M$6</f>
         <v>158986.54157771228</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="20"/>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="20"/>
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="17">
         <v>20719</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="17">
         <f>C5*Assumptions!$M$7</f>
         <v>24410.015842741999</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="17">
         <f>D5*Assumptions!$M$7</f>
         <v>25435.236508137164</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="17">
         <f>E5*Assumptions!$M$7</f>
         <v>26503.516441478925</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="17">
         <f>F5*Assumptions!$M$7</f>
         <v>27616.664132021036</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="17">
         <f>G5*Assumptions!$M$7</f>
         <v>28776.564025565924</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+      <c r="A8" s="14"/>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
     </row>
     <row r="9" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="17">
         <f>(B5-B7)</f>
         <v>112331</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="17">
         <f>C5-C7</f>
         <v>110451.950139258</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="17">
         <f t="shared" ref="D9:G9" si="0">D5-D7</f>
         <v>115090.93204510683</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="17">
         <f t="shared" si="0"/>
         <v>119924.75119100133</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="17">
         <f t="shared" si="0"/>
         <v>124961.59074102338</v>
       </c>
-      <c r="G9" s="24">
+      <c r="G9" s="17">
         <f t="shared" si="0"/>
         <v>130209.97755214636</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="17">
         <v>11698</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="18">
         <f>C3*Assumptions!$M$9</f>
         <v>12575.553098</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="18">
         <f>D3*Assumptions!$M$9</f>
         <v>13103.726328116001</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="18">
         <f>E3*Assumptions!$M$9</f>
         <v>13654.082833896873</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="18">
         <f>F3*Assumptions!$M$9</f>
         <v>14227.554312920542</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="18">
         <f>G3*Assumptions!$M$9</f>
         <v>14825.111594063206</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="17">
         <v>12715</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="19">
         <f>C3*Assumptions!$M$8</f>
         <v>12141.913336</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="19">
         <f>D3*Assumptions!$M$8</f>
         <v>12651.873696112001</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="19">
         <f>E3*Assumptions!$M$8</f>
         <v>13183.252391348704</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="19">
         <f>F3*Assumptions!$M$8</f>
         <v>13736.94899178535</v>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="19">
         <f>G3*Assumptions!$M$8</f>
         <v>14313.900849440335</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="18">
         <v>0</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="18">
         <f>(C3*Assumptions!$M$13)-(B3*Assumptions!$M$13)</f>
         <v>-1415.7797219999993</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="18">
         <f>(D3*Assumptions!$M$13)-(C3*Assumptions!$M$13)</f>
         <v>-1475.2424703240031</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="18">
         <f>(E3*Assumptions!$M$13)-(D3*Assumptions!$M$13)</f>
         <v>-1537.2026540776133</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="18">
         <f>(F3*Assumptions!$M$13)-(E3*Assumptions!$M$13)</f>
         <v>-1601.7651655488662</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="18">
         <f>(G3*Assumptions!$M$13)-(F3*Assumptions!$M$13)</f>
         <v>-1669.0393025019221</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
+      <c r="A16" s="16"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="33">
+      <c r="B17" s="24">
         <f>B9+B11-B13-B15</f>
         <v>111314</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="24">
         <f t="shared" ref="C17:G17" si="1">C9+C11-C13-C15</f>
         <v>112301.36962325801</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="24">
         <f t="shared" si="1"/>
         <v>117018.02714743483</v>
       </c>
-      <c r="E17" s="33">
+      <c r="E17" s="24">
         <f t="shared" si="1"/>
         <v>121932.78428762712</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="24">
         <f t="shared" si="1"/>
         <v>127053.96122770742</v>
       </c>
-      <c r="G17" s="33">
+      <c r="G17" s="24">
         <f t="shared" si="1"/>
         <v>132390.22759927114</v>
       </c>
@@ -1621,386 +1843,358 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U26"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="20"/>
-      <c r="B1" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="56"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="61"/>
-      <c r="J1" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="59"/>
-      <c r="L1" s="48"/>
-      <c r="M1" s="58"/>
-      <c r="Q1" s="48" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" s="48"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-    </row>
-    <row r="2" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="45"/>
+      <c r="B1" s="45" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="46"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="48"/>
+      <c r="J1" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="K1" s="49"/>
+      <c r="L1" s="45"/>
+      <c r="Q1" s="45" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="45"/>
+    </row>
+    <row r="2" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="43" t="s">
+      <c r="E2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="60" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="J3" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="24">
+    </row>
+    <row r="3" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="J3" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="17">
         <f>E14</f>
         <v>478091.6986563236</v>
       </c>
-      <c r="Q3" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="25">
+      <c r="Q3" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="R3" s="18">
         <f>L20</f>
         <v>2466855</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="23">
+      <c r="B4" s="14"/>
+      <c r="C4" s="17">
         <f>Forecast!C17</f>
         <v>112301.36962325801</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="42">
         <f>1/(1+Assumptions!M10)^1</f>
         <v>0.92165898617511521</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="17">
         <f>C4*D4</f>
         <v>103503.56647304886</v>
       </c>
-      <c r="J4" s="20"/>
-      <c r="K4" s="20"/>
-      <c r="L4" s="20"/>
-      <c r="Q4" s="20"/>
-      <c r="R4" s="20"/>
-    </row>
-    <row r="5" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="J5" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="35">
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
+      <c r="L4" s="14"/>
+      <c r="Q4" s="14"/>
+      <c r="R4" s="14"/>
+    </row>
+    <row r="5" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="17"/>
+      <c r="J5" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" s="17">
         <f>C26</f>
         <v>1504110.8804472487</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="21">
+      <c r="R5" s="15">
         <f>Assumptions!M12</f>
         <v>14900</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="23">
+      <c r="B6" s="14"/>
+      <c r="C6" s="17">
         <f>Forecast!D17</f>
         <v>117018.02714743483</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="42">
         <f>1/(1+Assumptions!M10)^2</f>
         <v>0.84945528679734128</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="17">
         <f>C6*D6</f>
         <v>99401.58181098332</v>
       </c>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-    </row>
-    <row r="7" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
-      <c r="J7" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" s="20"/>
-      <c r="L7" s="25">
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+    </row>
+    <row r="7" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="17"/>
+      <c r="J7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="18">
         <f>L3+L5</f>
         <v>1982202.5791035723</v>
       </c>
-      <c r="Q7" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="R7" s="26">
+      <c r="Q7" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="R7" s="19">
         <f>R3/R5</f>
         <v>165.56073825503356</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23">
+      <c r="B8" s="14"/>
+      <c r="C8" s="17">
         <f>Forecast!E17</f>
         <v>121932.78428762712</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="42">
         <f>1/(1+Assumptions!M10)^3</f>
         <v>0.78290809843072917</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="17">
         <f>C8*D8</f>
         <v>95462.164282990445</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A9" s="20"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="17"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20">
+      <c r="B10" s="14"/>
+      <c r="C10" s="17">
         <f>Forecast!F17</f>
         <v>127053.96122770742</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="42">
         <f>1/(1+Assumptions!M10)^4</f>
         <v>0.72157428426795334</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="17">
         <f>C10*D10</f>
         <v>91678.871136291273</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A11" s="20"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="20"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="17"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="20"/>
-      <c r="C12" s="23">
+      <c r="B12" s="14"/>
+      <c r="C12" s="17">
         <f>Forecast!G17</f>
         <v>132390.22759927114</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="42">
         <f>1/(1+Assumptions!M10)^5</f>
         <v>0.66504542328843619</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="17">
         <f>C12*D12</f>
         <v>88045.514953009682</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="34">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="38"/>
+      <c r="B14" s="38" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="43">
         <f>SUM(E4:E12)</f>
         <v>478091.6986563236</v>
       </c>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A16" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="58"/>
-      <c r="J16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="18" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="35">
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
+      <c r="J16" s="55" t="s">
+        <v>45</v>
+      </c>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
+      <c r="N16" s="55"/>
+    </row>
+    <row r="18" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="25">
         <v>172129</v>
       </c>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="J18" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="K18" s="20"/>
-      <c r="L18" s="25">
+      <c r="J18" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="K18" s="14"/>
+      <c r="L18" s="18">
         <f>L7</f>
         <v>1982202.5791035723</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-    </row>
-    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="36">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+    </row>
+    <row r="20" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="26">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="J20" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="24">
+      <c r="J20" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" s="17">
         <v>2466855</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="L21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="20" t="s">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="L21" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="20"/>
-      <c r="C22" s="36">
+      <c r="B22" s="14"/>
+      <c r="C22" s="26">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-    </row>
-    <row r="24" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="37">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="14"/>
+      <c r="C24" s="44">
         <f>(Forecast!G17*(1+'Discounted Cash Flow Valuation'!C20))/('Discounted Cash Flow Valuation'!C22-'Discounted Cash Flow Valuation'!C20)</f>
         <v>2261666.3881542152</v>
       </c>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-    </row>
-    <row r="26" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="38">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+    </row>
+    <row r="26" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="14"/>
+      <c r="C26" s="27">
         <f>C24/(1+C22)^5</f>
         <v>1504110.8804472487</v>
       </c>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="B14:D14"/>
     <mergeCell ref="J14:N14"/>
     <mergeCell ref="J16:N16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="51" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2013,196 +2207,188 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="26">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="C2" s="14"/>
+    </row>
+    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="26">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C3" s="14"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="K5" s="52" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="36">
-        <v>8.5000000000000006E-2</v>
-      </c>
-      <c r="C2" s="20"/>
-    </row>
-    <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="36">
-        <v>2.5000000000000001E-2</v>
-      </c>
-      <c r="C3" s="20"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="39" t="s">
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+    </row>
+    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="28">
+        <v>165.56</v>
+      </c>
+      <c r="H6" t="s">
+        <v>104</v>
+      </c>
+      <c r="K6" s="51" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="51"/>
+      <c r="M6" s="51"/>
+      <c r="N6" s="51"/>
+      <c r="O6" s="51"/>
+      <c r="P6" s="12"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="16"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+    </row>
+    <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="28">
+        <v>335.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="16"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+    </row>
+    <row r="10" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="2"/>
-      <c r="K5" s="39" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
-    </row>
-    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="40">
-        <v>165.56</v>
-      </c>
-      <c r="K6" s="52" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="52"/>
-      <c r="M6" s="52"/>
-      <c r="N6" s="52"/>
-      <c r="O6" s="52"/>
-      <c r="P6" s="18"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-    </row>
-    <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="40">
-        <v>335.52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="49">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="31">
         <f>(D6-D8)/D8</f>
         <v>-0.50655698617072009</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="74" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" s="75"/>
+      <c r="C12" s="75"/>
+      <c r="D12" s="76"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="46"/>
-      <c r="D12" s="47"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47"/>
+      <c r="B14" s="72"/>
+      <c r="C14" s="72"/>
+      <c r="D14" s="73"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="43"/>
-      <c r="B15" s="45" t="s">
+      <c r="A15" s="30"/>
+      <c r="B15" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="73"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="41">
+      <c r="B16" s="29">
         <v>0.02</v>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="26">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="29">
         <v>0.03</v>
       </c>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36">
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="26">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="28">
         <v>149.13</v>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="28">
         <v>161.22999999999999</v>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="28">
         <v>176.01</v>
       </c>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36">
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="26">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="28">
         <v>127.08</v>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="28">
         <v>165.56</v>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="28">
         <v>144.88</v>
       </c>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="26">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="28">
         <v>111.11</v>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="28">
         <v>117</v>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="28">
         <v>123.79</v>
       </c>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="K6:O6"/>
+    <mergeCell ref="K5:O5"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="B15:D15"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A12:D12"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="K6:O6"/>
-    <mergeCell ref="K5:O5"/>
-    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="67" orientation="portrait" r:id="rId1"/>
@@ -2222,268 +2408,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="52" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="I1" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="J3" s="54" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="54"/>
+      <c r="R3" s="54"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
+      <c r="O4" s="54"/>
+      <c r="P4" s="54"/>
+      <c r="Q4" s="54"/>
+      <c r="R4" s="54"/>
+    </row>
+    <row r="5" spans="1:18" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H5" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
+      <c r="K5" s="54"/>
+      <c r="L5" s="54"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="54"/>
+      <c r="O5" s="54"/>
+      <c r="P5" s="54"/>
+      <c r="Q5" s="54"/>
+      <c r="R5" s="54"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="54"/>
+      <c r="P6" s="54"/>
+      <c r="Q6" s="54"/>
+      <c r="R6" s="54"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="I1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="52" t="s">
-        <v>82</v>
-      </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="52"/>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="J3" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="J7" s="54"/>
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="54"/>
+      <c r="O7" s="54"/>
+      <c r="P7" s="54"/>
+      <c r="Q7" s="54"/>
+      <c r="R7" s="54"/>
+    </row>
+    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="50" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="39" t="s">
+      <c r="B8" s="51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-    </row>
-    <row r="8" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="B10" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="57"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="12"/>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="52" t="s">
+      <c r="B13" s="51" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="53" t="s">
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="32"/>
+    </row>
+    <row r="16" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="50" t="s">
         <v>66</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="B16" s="51" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="52"/>
-      <c r="D10" s="52"/>
-      <c r="E10" s="52"/>
-      <c r="F10" s="52"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13" s="52" t="s">
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="62" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="52"/>
-      <c r="B14" s="52"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="50"/>
-    </row>
-    <row r="16" spans="1:18" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="52" t="s">
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="39" t="s">
+      <c r="B20" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="20"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="39" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+      <c r="E20" s="51"/>
+      <c r="F20" s="51"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="59"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="B20" s="55" t="s">
+      <c r="B23" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="39"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+      <c r="C23" s="51"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
+      <c r="F23" s="51"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="61"/>
+      <c r="B24" s="51"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="51"/>
+      <c r="E24" s="51"/>
+      <c r="F24" s="51"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="59" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="52" t="s">
+      <c r="B26" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="44"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="39" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="C26" s="52"/>
-      <c r="D26" s="52"/>
-      <c r="E26" s="52"/>
-      <c r="F26" s="52"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="39"/>
-      <c r="B27" s="52"/>
-      <c r="C27" s="52"/>
-      <c r="D27" s="52"/>
-      <c r="E27" s="52"/>
-      <c r="F27" s="52"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="51"/>
+      <c r="C27" s="51"/>
+      <c r="D27" s="51"/>
+      <c r="E27" s="51"/>
+      <c r="F27" s="51"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="B23:F24"/>
+  <mergeCells count="20">
     <mergeCell ref="B26:F27"/>
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="J3:R7"/>
@@ -2502,6 +2691,8 @@
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="A6:F6"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="B23:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="52" orientation="portrait" r:id="rId1"/>
@@ -2517,51 +2708,51 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="4" spans="9:10" ht="33.6" x14ac:dyDescent="0.65">
-      <c r="I4" s="62" t="s">
-        <v>83</v>
+      <c r="I4" s="34" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J12" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I13" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="9:10" x14ac:dyDescent="0.3">
       <c r="I16" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.3">
       <c r="I17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
